--- a/NOC_EndUser_CSAT.xlsx
+++ b/NOC_EndUser_CSAT.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30431"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chilutej\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92230CBE-44A0-4D69-AEB0-3C6623379592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{92230CBE-44A0-4D69-AEB0-3C6623379592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A70C2642-3991-4552-B80E-3D3046C3BC43}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2142,7 +2142,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:D375"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -2166,7 +2165,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="2" spans="1:4" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -2180,7 +2179,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="3" spans="1:4" ht="15" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -2194,7 +2193,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="4" spans="1:4" ht="15" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -2208,7 +2207,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="5" spans="1:4" ht="15" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -2222,7 +2221,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="6" spans="1:4" ht="15" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
@@ -2236,7 +2235,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="7" spans="1:4" ht="15" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>15</v>
       </c>
@@ -2250,7 +2249,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="8" spans="1:4" ht="15" customHeight="1">
       <c r="A8" s="2" t="s">
         <v>17</v>
       </c>
@@ -2264,7 +2263,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="9" spans="1:4" ht="15" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>19</v>
       </c>
@@ -2278,7 +2277,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="10" spans="1:4" ht="15" customHeight="1">
       <c r="A10" s="2" t="s">
         <v>21</v>
       </c>
@@ -2292,7 +2291,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="11" spans="1:4" ht="15" customHeight="1">
       <c r="A11" s="2" t="s">
         <v>23</v>
       </c>
@@ -2306,7 +2305,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="12" spans="1:4" ht="15" customHeight="1">
       <c r="A12" s="2" t="s">
         <v>24</v>
       </c>
@@ -2320,7 +2319,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="13" spans="1:4" ht="15" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>26</v>
       </c>
@@ -2334,7 +2333,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="14" spans="1:4" ht="15" customHeight="1">
       <c r="A14" s="2" t="s">
         <v>28</v>
       </c>
@@ -2348,7 +2347,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="15" spans="1:4" ht="15" customHeight="1">
       <c r="A15" s="2" t="s">
         <v>30</v>
       </c>
@@ -2362,7 +2361,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="16" spans="1:4" ht="15" customHeight="1">
       <c r="A16" s="2" t="s">
         <v>32</v>
       </c>
@@ -2376,7 +2375,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="17" spans="1:4" ht="15" customHeight="1">
       <c r="A17" s="2" t="s">
         <v>33</v>
       </c>
@@ -2390,7 +2389,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="18" spans="1:4" ht="15" customHeight="1">
       <c r="A18" s="2" t="s">
         <v>34</v>
       </c>
@@ -2404,7 +2403,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="19" spans="1:4" ht="15" customHeight="1">
       <c r="A19" s="2" t="s">
         <v>36</v>
       </c>
@@ -2418,7 +2417,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="20" spans="1:4" ht="15" customHeight="1">
       <c r="A20" s="2" t="s">
         <v>37</v>
       </c>
@@ -2432,7 +2431,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="21" spans="1:4" ht="15" customHeight="1">
       <c r="A21" s="2" t="s">
         <v>39</v>
       </c>
@@ -2446,7 +2445,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="22" spans="1:4" ht="15" customHeight="1">
       <c r="A22" s="2" t="s">
         <v>40</v>
       </c>
@@ -2460,7 +2459,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="23" spans="1:4" ht="15" customHeight="1">
       <c r="A23" s="2" t="s">
         <v>42</v>
       </c>
@@ -2474,7 +2473,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="24" spans="1:4" ht="15" customHeight="1">
       <c r="A24" s="2" t="s">
         <v>44</v>
       </c>
@@ -2488,7 +2487,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="25" spans="1:4" ht="15" customHeight="1">
       <c r="A25" s="2" t="s">
         <v>46</v>
       </c>
@@ -2502,7 +2501,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="26" spans="1:4" ht="15" customHeight="1">
       <c r="A26" s="2" t="s">
         <v>48</v>
       </c>
@@ -2516,7 +2515,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="27" spans="1:4" ht="15" customHeight="1">
       <c r="A27" s="2" t="s">
         <v>50</v>
       </c>
@@ -2530,7 +2529,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="28" spans="1:4" ht="15" customHeight="1">
       <c r="A28" s="2" t="s">
         <v>52</v>
       </c>
@@ -2544,7 +2543,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="29" spans="1:4" ht="15" customHeight="1">
       <c r="A29" s="2" t="s">
         <v>54</v>
       </c>
@@ -2558,7 +2557,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="30" spans="1:4" ht="15" customHeight="1">
       <c r="A30" s="2" t="s">
         <v>56</v>
       </c>
@@ -2572,7 +2571,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="31" spans="1:4" ht="15" customHeight="1">
       <c r="A31" s="2" t="s">
         <v>58</v>
       </c>
@@ -2586,7 +2585,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="32" spans="1:4" ht="15" customHeight="1">
       <c r="A32" s="2" t="s">
         <v>60</v>
       </c>
@@ -2600,7 +2599,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="33" spans="1:4" ht="15" customHeight="1">
       <c r="A33" s="2" t="s">
         <v>62</v>
       </c>
@@ -2614,7 +2613,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="34" spans="1:4" ht="15" customHeight="1">
       <c r="A34" s="2" t="s">
         <v>63</v>
       </c>
@@ -2628,7 +2627,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="35" spans="1:4" ht="15" customHeight="1">
       <c r="A35" s="2" t="s">
         <v>65</v>
       </c>
@@ -2642,7 +2641,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="36" spans="1:4" ht="15" customHeight="1">
       <c r="A36" s="2" t="s">
         <v>66</v>
       </c>
@@ -2656,7 +2655,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="37" spans="1:4" ht="15" customHeight="1">
       <c r="A37" s="2" t="s">
         <v>68</v>
       </c>
@@ -2670,7 +2669,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="38" spans="1:4" ht="15" customHeight="1">
       <c r="A38" s="2" t="s">
         <v>69</v>
       </c>
@@ -2684,7 +2683,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="39" spans="1:4" ht="15" customHeight="1">
       <c r="A39" s="2" t="s">
         <v>70</v>
       </c>
@@ -2698,7 +2697,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="40" spans="1:4" ht="15" customHeight="1">
       <c r="A40" s="2" t="s">
         <v>71</v>
       </c>
@@ -2712,7 +2711,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="41" spans="1:4" ht="15" customHeight="1">
       <c r="A41" s="2" t="s">
         <v>72</v>
       </c>
@@ -2726,7 +2725,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="42" spans="1:4" ht="15" customHeight="1">
       <c r="A42" s="2" t="s">
         <v>74</v>
       </c>
@@ -2740,7 +2739,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="43" spans="1:4" ht="15" customHeight="1">
       <c r="A43" s="2" t="s">
         <v>75</v>
       </c>
@@ -2754,7 +2753,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="44" spans="1:4" ht="15" customHeight="1">
       <c r="A44" s="2" t="s">
         <v>76</v>
       </c>
@@ -2768,7 +2767,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="45" spans="1:4" ht="15" customHeight="1">
       <c r="A45" s="2" t="s">
         <v>77</v>
       </c>
@@ -2782,7 +2781,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="46" spans="1:4" ht="15" customHeight="1">
       <c r="A46" s="2" t="s">
         <v>79</v>
       </c>
@@ -2796,7 +2795,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="47" spans="1:4" ht="15" customHeight="1">
       <c r="A47" s="2" t="s">
         <v>80</v>
       </c>
@@ -2810,7 +2809,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="48" spans="1:4" ht="15" customHeight="1">
       <c r="A48" s="2" t="s">
         <v>82</v>
       </c>
@@ -2824,7 +2823,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="49" spans="1:4" ht="15" customHeight="1">
       <c r="A49" s="2" t="s">
         <v>84</v>
       </c>
@@ -2838,7 +2837,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="50" spans="1:4" ht="15" customHeight="1">
       <c r="A50" s="2" t="s">
         <v>86</v>
       </c>
@@ -2852,7 +2851,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="51" spans="1:4" ht="15" customHeight="1">
       <c r="A51" s="2" t="s">
         <v>88</v>
       </c>
@@ -2866,7 +2865,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="52" spans="1:4" ht="15" customHeight="1">
       <c r="A52" s="2" t="s">
         <v>89</v>
       </c>
@@ -2880,7 +2879,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="53" spans="1:4" ht="15" customHeight="1">
       <c r="A53" s="2" t="s">
         <v>91</v>
       </c>
@@ -2894,7 +2893,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="54" spans="1:4" ht="15" customHeight="1">
       <c r="A54" s="2" t="s">
         <v>92</v>
       </c>
@@ -2908,7 +2907,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="55" spans="1:4" ht="15" customHeight="1">
       <c r="A55" s="2" t="s">
         <v>93</v>
       </c>
@@ -2922,7 +2921,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="56" spans="1:4" ht="15" customHeight="1">
       <c r="A56" s="2" t="s">
         <v>94</v>
       </c>
@@ -2936,7 +2935,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="57" spans="1:4" ht="15" customHeight="1">
       <c r="A57" s="2" t="s">
         <v>95</v>
       </c>
@@ -2950,7 +2949,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="58" spans="1:4" ht="15" customHeight="1">
       <c r="A58" s="2" t="s">
         <v>97</v>
       </c>
@@ -2964,7 +2963,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="59" spans="1:4" ht="15" customHeight="1">
       <c r="A59" s="2" t="s">
         <v>98</v>
       </c>
@@ -2978,7 +2977,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="60" spans="1:4" ht="15" customHeight="1">
       <c r="A60" s="2" t="s">
         <v>100</v>
       </c>
@@ -2992,7 +2991,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="61" spans="1:4" ht="15" customHeight="1">
       <c r="A61" s="2" t="s">
         <v>101</v>
       </c>
@@ -3006,7 +3005,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="62" spans="1:4" ht="15" customHeight="1">
       <c r="A62" s="2" t="s">
         <v>103</v>
       </c>
@@ -3020,7 +3019,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="63" spans="1:4" ht="15" customHeight="1">
       <c r="A63" s="2" t="s">
         <v>104</v>
       </c>
@@ -3034,7 +3033,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="64" spans="1:4" ht="15" customHeight="1">
       <c r="A64" s="2" t="s">
         <v>105</v>
       </c>
@@ -3048,7 +3047,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="65" spans="1:4" ht="15" customHeight="1">
       <c r="A65" s="2" t="s">
         <v>106</v>
       </c>
@@ -3062,7 +3061,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="66" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="66" spans="1:4" ht="15" customHeight="1">
       <c r="A66" s="2" t="s">
         <v>107</v>
       </c>
@@ -3076,7 +3075,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="67" spans="1:4" ht="15" customHeight="1">
       <c r="A67" s="2" t="s">
         <v>108</v>
       </c>
@@ -3090,7 +3089,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="68" spans="1:4" ht="15" customHeight="1">
       <c r="A68" s="2" t="s">
         <v>110</v>
       </c>
@@ -3104,7 +3103,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="69" spans="1:4" ht="15" customHeight="1">
       <c r="A69" s="2" t="s">
         <v>111</v>
       </c>
@@ -3118,7 +3117,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="70" spans="1:4" ht="15" customHeight="1">
       <c r="A70" s="2" t="s">
         <v>112</v>
       </c>
@@ -3132,7 +3131,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="71" spans="1:4" ht="15" customHeight="1">
       <c r="A71" s="2" t="s">
         <v>113</v>
       </c>
@@ -3146,7 +3145,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="72" spans="1:4" ht="15" customHeight="1">
       <c r="A72" s="2" t="s">
         <v>114</v>
       </c>
@@ -3160,7 +3159,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="73" spans="1:4" ht="15" customHeight="1">
       <c r="A73" s="2" t="s">
         <v>115</v>
       </c>
@@ -3174,7 +3173,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="74" spans="1:4" ht="15" customHeight="1">
       <c r="A74" s="2" t="s">
         <v>116</v>
       </c>
@@ -3188,7 +3187,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="75" spans="1:4" ht="15" customHeight="1">
       <c r="A75" s="2" t="s">
         <v>118</v>
       </c>
@@ -3202,7 +3201,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="76" spans="1:4" ht="15" customHeight="1">
       <c r="A76" s="2" t="s">
         <v>119</v>
       </c>
@@ -3216,7 +3215,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="77" spans="1:4" ht="15" customHeight="1">
       <c r="A77" s="2" t="s">
         <v>120</v>
       </c>
@@ -3230,7 +3229,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="78" spans="1:4" ht="15" customHeight="1">
       <c r="A78" s="2" t="s">
         <v>121</v>
       </c>
@@ -3244,7 +3243,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="79" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="79" spans="1:4" ht="15" customHeight="1">
       <c r="A79" s="2" t="s">
         <v>122</v>
       </c>
@@ -3258,7 +3257,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="80" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="80" spans="1:4" ht="15" customHeight="1">
       <c r="A80" s="2" t="s">
         <v>124</v>
       </c>
@@ -3272,7 +3271,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="81" spans="1:4" ht="15" customHeight="1">
       <c r="A81" s="2" t="s">
         <v>126</v>
       </c>
@@ -3286,7 +3285,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="82" spans="1:4" ht="15" customHeight="1">
       <c r="A82" s="2" t="s">
         <v>128</v>
       </c>
@@ -3300,7 +3299,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="83" spans="1:4" ht="15" customHeight="1">
       <c r="A83" s="2" t="s">
         <v>129</v>
       </c>
@@ -3314,7 +3313,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="84" spans="1:4" ht="15" customHeight="1">
       <c r="A84" s="2" t="s">
         <v>130</v>
       </c>
@@ -3328,7 +3327,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="85" spans="1:4" ht="15" customHeight="1">
       <c r="A85" s="2" t="s">
         <v>132</v>
       </c>
@@ -3342,7 +3341,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="86" spans="1:4" ht="15" customHeight="1">
       <c r="A86" s="2" t="s">
         <v>133</v>
       </c>
@@ -3356,7 +3355,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="87" spans="1:4" ht="15" customHeight="1">
       <c r="A87" s="2" t="s">
         <v>134</v>
       </c>
@@ -3370,7 +3369,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="88" spans="1:4" ht="15" customHeight="1">
       <c r="A88" s="2" t="s">
         <v>135</v>
       </c>
@@ -3384,7 +3383,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="89" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="89" spans="1:4" ht="15" customHeight="1">
       <c r="A89" s="2" t="s">
         <v>136</v>
       </c>
@@ -3398,7 +3397,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="90" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="90" spans="1:4" ht="15" customHeight="1">
       <c r="A90" s="2" t="s">
         <v>138</v>
       </c>
@@ -3412,7 +3411,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="91" spans="1:4" ht="15" customHeight="1">
       <c r="A91" s="2" t="s">
         <v>140</v>
       </c>
@@ -3426,7 +3425,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="92" spans="1:4" ht="15" customHeight="1">
       <c r="A92" s="2" t="s">
         <v>142</v>
       </c>
@@ -3440,7 +3439,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="93" spans="1:4" ht="15" customHeight="1">
       <c r="A93" s="2" t="s">
         <v>143</v>
       </c>
@@ -3454,7 +3453,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="94" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="94" spans="1:4" ht="15" customHeight="1">
       <c r="A94" s="2" t="s">
         <v>145</v>
       </c>
@@ -3468,7 +3467,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="95" spans="1:4" ht="15" customHeight="1">
       <c r="A95" s="2" t="s">
         <v>146</v>
       </c>
@@ -3482,7 +3481,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="96" spans="1:4" ht="15" customHeight="1">
       <c r="A96" s="2" t="s">
         <v>147</v>
       </c>
@@ -3496,7 +3495,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="97" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="97" spans="1:4" ht="15" customHeight="1">
       <c r="A97" s="2" t="s">
         <v>149</v>
       </c>
@@ -3510,7 +3509,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="98" spans="1:4" ht="15" customHeight="1">
       <c r="A98" s="2" t="s">
         <v>150</v>
       </c>
@@ -3524,7 +3523,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="99" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="99" spans="1:4" ht="15" customHeight="1">
       <c r="A99" s="2" t="s">
         <v>151</v>
       </c>
@@ -3538,7 +3537,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="100" spans="1:4" ht="15" customHeight="1">
       <c r="A100" s="2" t="s">
         <v>152</v>
       </c>
@@ -3552,7 +3551,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="101" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="101" spans="1:4" ht="15" customHeight="1">
       <c r="A101" s="2" t="s">
         <v>154</v>
       </c>
@@ -3566,7 +3565,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="102" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="102" spans="1:4" ht="15" customHeight="1">
       <c r="A102" s="2" t="s">
         <v>156</v>
       </c>
@@ -3580,7 +3579,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="103" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="103" spans="1:4" ht="15" customHeight="1">
       <c r="A103" s="2" t="s">
         <v>158</v>
       </c>
@@ -3594,7 +3593,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="104" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="104" spans="1:4" ht="15" customHeight="1">
       <c r="A104" s="2" t="s">
         <v>159</v>
       </c>
@@ -3608,7 +3607,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="105" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="105" spans="1:4" ht="15" customHeight="1">
       <c r="A105" s="2" t="s">
         <v>161</v>
       </c>
@@ -3622,7 +3621,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="106" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="106" spans="1:4" ht="15" customHeight="1">
       <c r="A106" s="2" t="s">
         <v>163</v>
       </c>
@@ -3636,7 +3635,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="107" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="107" spans="1:4" ht="15" customHeight="1">
       <c r="A107" s="2" t="s">
         <v>164</v>
       </c>
@@ -3650,7 +3649,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="108" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="108" spans="1:4" ht="15" customHeight="1">
       <c r="A108" s="2" t="s">
         <v>166</v>
       </c>
@@ -3664,7 +3663,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="109" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="109" spans="1:4" ht="15" customHeight="1">
       <c r="A109" s="2" t="s">
         <v>167</v>
       </c>
@@ -3678,7 +3677,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="110" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="110" spans="1:4" ht="15" customHeight="1">
       <c r="A110" s="2" t="s">
         <v>169</v>
       </c>
@@ -3692,7 +3691,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="111" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="111" spans="1:4" ht="15" customHeight="1">
       <c r="A111" s="2" t="s">
         <v>170</v>
       </c>
@@ -3706,7 +3705,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="112" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="112" spans="1:4" ht="15" customHeight="1">
       <c r="A112" s="2" t="s">
         <v>171</v>
       </c>
@@ -3720,7 +3719,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="113" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="113" spans="1:4" ht="15" customHeight="1">
       <c r="A113" s="2" t="s">
         <v>172</v>
       </c>
@@ -3734,7 +3733,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="114" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="114" spans="1:4" ht="15" customHeight="1">
       <c r="A114" s="2" t="s">
         <v>174</v>
       </c>
@@ -3748,7 +3747,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="115" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="115" spans="1:4" ht="15" customHeight="1">
       <c r="A115" s="2" t="s">
         <v>176</v>
       </c>
@@ -3762,7 +3761,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="116" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="116" spans="1:4" ht="15" customHeight="1">
       <c r="A116" s="2" t="s">
         <v>178</v>
       </c>
@@ -3776,7 +3775,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="117" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="117" spans="1:4" ht="15" customHeight="1">
       <c r="A117" s="2" t="s">
         <v>179</v>
       </c>
@@ -3790,7 +3789,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="118" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="118" spans="1:4" ht="15" customHeight="1">
       <c r="A118" s="2" t="s">
         <v>181</v>
       </c>
@@ -3804,7 +3803,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="119" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="119" spans="1:4" ht="15" customHeight="1">
       <c r="A119" s="2" t="s">
         <v>182</v>
       </c>
@@ -3818,7 +3817,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="120" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="120" spans="1:4" ht="15" customHeight="1">
       <c r="A120" s="2" t="s">
         <v>184</v>
       </c>
@@ -3832,7 +3831,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="121" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="121" spans="1:4" ht="15" customHeight="1">
       <c r="A121" s="2" t="s">
         <v>186</v>
       </c>
@@ -3846,7 +3845,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="122" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="122" spans="1:4" ht="15" customHeight="1">
       <c r="A122" s="2" t="s">
         <v>187</v>
       </c>
@@ -3860,7 +3859,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="123" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="123" spans="1:4" ht="15" customHeight="1">
       <c r="A123" s="2" t="s">
         <v>189</v>
       </c>
@@ -3874,7 +3873,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="124" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="124" spans="1:4" ht="15" customHeight="1">
       <c r="A124" s="2" t="s">
         <v>191</v>
       </c>
@@ -3888,7 +3887,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="125" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="125" spans="1:4" ht="15" customHeight="1">
       <c r="A125" s="2" t="s">
         <v>192</v>
       </c>
@@ -3902,7 +3901,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="126" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="126" spans="1:4" ht="15" customHeight="1">
       <c r="A126" s="2" t="s">
         <v>193</v>
       </c>
@@ -3916,7 +3915,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="127" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="127" spans="1:4" ht="15" customHeight="1">
       <c r="A127" s="2" t="s">
         <v>195</v>
       </c>
@@ -3930,7 +3929,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="128" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="128" spans="1:4" ht="15" customHeight="1">
       <c r="A128" s="2" t="s">
         <v>196</v>
       </c>
@@ -3944,7 +3943,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="129" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="129" spans="1:4" ht="15" customHeight="1">
       <c r="A129" s="2" t="s">
         <v>197</v>
       </c>
@@ -3958,7 +3957,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="130" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="130" spans="1:4" ht="15" customHeight="1">
       <c r="A130" s="2" t="s">
         <v>199</v>
       </c>
@@ -3972,7 +3971,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="131" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="131" spans="1:4" ht="15" customHeight="1">
       <c r="A131" s="2" t="s">
         <v>200</v>
       </c>
@@ -3986,7 +3985,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="132" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="132" spans="1:4" ht="15" customHeight="1">
       <c r="A132" s="2" t="s">
         <v>202</v>
       </c>
@@ -4000,7 +3999,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="133" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="133" spans="1:4" ht="15" customHeight="1">
       <c r="A133" s="2" t="s">
         <v>203</v>
       </c>
@@ -4014,7 +4013,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="134" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="134" spans="1:4" ht="15" customHeight="1">
       <c r="A134" s="2" t="s">
         <v>205</v>
       </c>
@@ -4028,7 +4027,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="135" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="135" spans="1:4" ht="15" customHeight="1">
       <c r="A135" s="2" t="s">
         <v>206</v>
       </c>
@@ -4042,7 +4041,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="136" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="136" spans="1:4" ht="15" customHeight="1">
       <c r="A136" s="2" t="s">
         <v>208</v>
       </c>
@@ -4056,7 +4055,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="137" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="137" spans="1:4" ht="15" customHeight="1">
       <c r="A137" s="2" t="s">
         <v>209</v>
       </c>
@@ -4070,7 +4069,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="138" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="138" spans="1:4" ht="15" customHeight="1">
       <c r="A138" s="2" t="s">
         <v>210</v>
       </c>
@@ -4084,7 +4083,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="139" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="139" spans="1:4" ht="15" customHeight="1">
       <c r="A139" s="2" t="s">
         <v>211</v>
       </c>
@@ -4098,7 +4097,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="140" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="140" spans="1:4" ht="15" customHeight="1">
       <c r="A140" s="2" t="s">
         <v>212</v>
       </c>
@@ -4112,7 +4111,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="141" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="141" spans="1:4" ht="15" customHeight="1">
       <c r="A141" s="2" t="s">
         <v>213</v>
       </c>
@@ -4126,7 +4125,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="142" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="142" spans="1:4" ht="15" customHeight="1">
       <c r="A142" s="2" t="s">
         <v>215</v>
       </c>
@@ -4140,7 +4139,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="143" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="143" spans="1:4" ht="15" customHeight="1">
       <c r="A143" s="2" t="s">
         <v>216</v>
       </c>
@@ -4154,7 +4153,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="144" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="144" spans="1:4" ht="15" customHeight="1">
       <c r="A144" s="2" t="s">
         <v>217</v>
       </c>
@@ -4168,7 +4167,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="145" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="145" spans="1:4" ht="15" customHeight="1">
       <c r="A145" s="2" t="s">
         <v>218</v>
       </c>
@@ -4182,7 +4181,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="146" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="146" spans="1:4" ht="15" customHeight="1">
       <c r="A146" s="2" t="s">
         <v>219</v>
       </c>
@@ -4196,7 +4195,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="147" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="147" spans="1:4" ht="15" customHeight="1">
       <c r="A147" s="2" t="s">
         <v>220</v>
       </c>
@@ -4210,7 +4209,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="148" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="148" spans="1:4" ht="15" customHeight="1">
       <c r="A148" s="2" t="s">
         <v>222</v>
       </c>
@@ -4224,7 +4223,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="149" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="149" spans="1:4" ht="15" customHeight="1">
       <c r="A149" s="2" t="s">
         <v>223</v>
       </c>
@@ -4238,7 +4237,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="150" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="150" spans="1:4" ht="15" customHeight="1">
       <c r="A150" s="2" t="s">
         <v>224</v>
       </c>
@@ -4252,7 +4251,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="151" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="151" spans="1:4" ht="15" customHeight="1">
       <c r="A151" s="2" t="s">
         <v>226</v>
       </c>
@@ -4266,7 +4265,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="152" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="152" spans="1:4" ht="15" customHeight="1">
       <c r="A152" s="2" t="s">
         <v>227</v>
       </c>
@@ -4280,7 +4279,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="153" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="153" spans="1:4" ht="15" customHeight="1">
       <c r="A153" s="2" t="s">
         <v>229</v>
       </c>
@@ -4294,7 +4293,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="154" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="154" spans="1:4" ht="15" customHeight="1">
       <c r="A154" s="2" t="s">
         <v>230</v>
       </c>
@@ -4308,7 +4307,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="155" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="155" spans="1:4" ht="15" customHeight="1">
       <c r="A155" s="2" t="s">
         <v>231</v>
       </c>
@@ -4322,7 +4321,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="156" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="156" spans="1:4" ht="15" customHeight="1">
       <c r="A156" s="2" t="s">
         <v>232</v>
       </c>
@@ -4336,7 +4335,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="157" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="157" spans="1:4" ht="15" customHeight="1">
       <c r="A157" s="2" t="s">
         <v>233</v>
       </c>
@@ -4350,7 +4349,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="158" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="158" spans="1:4" ht="15" customHeight="1">
       <c r="A158" s="2" t="s">
         <v>234</v>
       </c>
@@ -4364,7 +4363,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="159" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="159" spans="1:4" ht="15" customHeight="1">
       <c r="A159" s="2" t="s">
         <v>235</v>
       </c>
@@ -4378,7 +4377,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="160" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="160" spans="1:4" ht="15" customHeight="1">
       <c r="A160" s="2" t="s">
         <v>236</v>
       </c>
@@ -4392,7 +4391,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="161" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="161" spans="1:4" ht="15" customHeight="1">
       <c r="A161" s="2" t="s">
         <v>237</v>
       </c>
@@ -4406,7 +4405,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="162" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="162" spans="1:4" ht="15" customHeight="1">
       <c r="A162" s="2" t="s">
         <v>238</v>
       </c>
@@ -4420,7 +4419,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="163" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="163" spans="1:4" ht="15" customHeight="1">
       <c r="A163" s="2" t="s">
         <v>239</v>
       </c>
@@ -4434,7 +4433,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="164" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="164" spans="1:4" ht="15" customHeight="1">
       <c r="A164" s="2" t="s">
         <v>240</v>
       </c>
@@ -4448,7 +4447,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="165" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="165" spans="1:4" ht="15" customHeight="1">
       <c r="A165" s="2" t="s">
         <v>242</v>
       </c>
@@ -4462,7 +4461,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="166" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="166" spans="1:4" ht="15" customHeight="1">
       <c r="A166" s="2" t="s">
         <v>243</v>
       </c>
@@ -4476,7 +4475,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="167" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="167" spans="1:4" ht="15" customHeight="1">
       <c r="A167" s="2" t="s">
         <v>245</v>
       </c>
@@ -4490,7 +4489,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="168" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="168" spans="1:4" ht="15" customHeight="1">
       <c r="A168" s="2" t="s">
         <v>247</v>
       </c>
@@ -4504,7 +4503,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="169" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="169" spans="1:4" ht="15" customHeight="1">
       <c r="A169" s="2" t="s">
         <v>249</v>
       </c>
@@ -4518,7 +4517,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="170" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="170" spans="1:4" ht="15" customHeight="1">
       <c r="A170" s="2" t="s">
         <v>250</v>
       </c>
@@ -4532,7 +4531,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="171" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="171" spans="1:4" ht="15" customHeight="1">
       <c r="A171" s="2" t="s">
         <v>251</v>
       </c>
@@ -4546,7 +4545,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="172" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="172" spans="1:4" ht="15" customHeight="1">
       <c r="A172" s="2" t="s">
         <v>253</v>
       </c>
@@ -4560,7 +4559,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="173" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="173" spans="1:4" ht="15" customHeight="1">
       <c r="A173" s="2" t="s">
         <v>255</v>
       </c>
@@ -4574,7 +4573,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="174" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="174" spans="1:4" ht="15" customHeight="1">
       <c r="A174" s="2" t="s">
         <v>256</v>
       </c>
@@ -4588,7 +4587,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="175" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="175" spans="1:4" ht="15" customHeight="1">
       <c r="A175" s="2" t="s">
         <v>257</v>
       </c>
@@ -4602,7 +4601,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="176" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="176" spans="1:4" ht="15" customHeight="1">
       <c r="A176" s="2" t="s">
         <v>258</v>
       </c>
@@ -4616,7 +4615,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="177" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="177" spans="1:4" ht="15" customHeight="1">
       <c r="A177" s="2" t="s">
         <v>259</v>
       </c>
@@ -4630,7 +4629,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="178" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="178" spans="1:4" ht="15" customHeight="1">
       <c r="A178" s="2" t="s">
         <v>260</v>
       </c>
@@ -4644,7 +4643,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="179" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="179" spans="1:4" ht="15" customHeight="1">
       <c r="A179" s="2" t="s">
         <v>261</v>
       </c>
@@ -4658,7 +4657,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="180" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="180" spans="1:4" ht="15" customHeight="1">
       <c r="A180" s="2" t="s">
         <v>262</v>
       </c>
@@ -4672,7 +4671,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="181" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="181" spans="1:4" ht="15" customHeight="1">
       <c r="A181" s="2" t="s">
         <v>263</v>
       </c>
@@ -4686,7 +4685,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="182" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="182" spans="1:4" ht="15" customHeight="1">
       <c r="A182" s="2" t="s">
         <v>264</v>
       </c>
@@ -4700,7 +4699,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="183" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="183" spans="1:4" ht="15" customHeight="1">
       <c r="A183" s="2" t="s">
         <v>266</v>
       </c>
@@ -4714,7 +4713,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="184" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="184" spans="1:4" ht="15" customHeight="1">
       <c r="A184" s="2" t="s">
         <v>267</v>
       </c>
@@ -4728,7 +4727,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="185" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="185" spans="1:4" ht="15" customHeight="1">
       <c r="A185" s="2" t="s">
         <v>268</v>
       </c>
@@ -4742,7 +4741,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="186" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="186" spans="1:4" ht="15" customHeight="1">
       <c r="A186" s="2" t="s">
         <v>270</v>
       </c>
@@ -4756,7 +4755,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="187" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="187" spans="1:4" ht="15" customHeight="1">
       <c r="A187" s="2" t="s">
         <v>271</v>
       </c>
@@ -4770,7 +4769,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="188" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="188" spans="1:4" ht="15" customHeight="1">
       <c r="A188" s="2" t="s">
         <v>273</v>
       </c>
@@ -4784,7 +4783,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="189" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="189" spans="1:4" ht="15" customHeight="1">
       <c r="A189" s="2" t="s">
         <v>275</v>
       </c>
@@ -4798,7 +4797,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="190" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="190" spans="1:4" ht="15" customHeight="1">
       <c r="A190" s="2" t="s">
         <v>276</v>
       </c>
@@ -4812,7 +4811,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="191" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="191" spans="1:4" ht="15" customHeight="1">
       <c r="A191" s="2" t="s">
         <v>278</v>
       </c>
@@ -4826,7 +4825,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="192" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="192" spans="1:4" ht="15" customHeight="1">
       <c r="A192" s="2" t="s">
         <v>279</v>
       </c>
@@ -4840,7 +4839,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="193" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="193" spans="1:4" ht="15" customHeight="1">
       <c r="A193" s="2" t="s">
         <v>280</v>
       </c>
@@ -4854,7 +4853,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="194" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="194" spans="1:4" ht="15" customHeight="1">
       <c r="A194" s="2" t="s">
         <v>281</v>
       </c>
@@ -4868,7 +4867,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="195" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="195" spans="1:4" ht="15" customHeight="1">
       <c r="A195" s="2" t="s">
         <v>282</v>
       </c>
@@ -4882,7 +4881,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="196" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="196" spans="1:4" ht="15" customHeight="1">
       <c r="A196" s="2" t="s">
         <v>283</v>
       </c>
@@ -4896,7 +4895,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="197" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="197" spans="1:4" ht="15" customHeight="1">
       <c r="A197" s="2" t="s">
         <v>284</v>
       </c>
@@ -4910,7 +4909,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="198" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="198" spans="1:4" ht="15" customHeight="1">
       <c r="A198" s="2" t="s">
         <v>285</v>
       </c>
@@ -4924,7 +4923,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="199" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="199" spans="1:4" ht="15" customHeight="1">
       <c r="A199" s="2" t="s">
         <v>286</v>
       </c>
@@ -4938,7 +4937,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="200" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="200" spans="1:4" ht="15" customHeight="1">
       <c r="A200" s="2" t="s">
         <v>288</v>
       </c>
@@ -4952,7 +4951,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="201" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="201" spans="1:4" ht="15" customHeight="1">
       <c r="A201" s="2" t="s">
         <v>289</v>
       </c>
@@ -4966,7 +4965,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="202" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="202" spans="1:4" ht="15" customHeight="1">
       <c r="A202" s="2" t="s">
         <v>291</v>
       </c>
@@ -4980,7 +4979,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="203" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="203" spans="1:4" ht="15" customHeight="1">
       <c r="A203" s="2" t="s">
         <v>292</v>
       </c>
@@ -4994,7 +4993,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="204" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="204" spans="1:4" ht="15" customHeight="1">
       <c r="A204" s="2" t="s">
         <v>294</v>
       </c>
@@ -5008,7 +5007,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="205" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="205" spans="1:4" ht="15" customHeight="1">
       <c r="A205" s="2" t="s">
         <v>295</v>
       </c>
@@ -5022,7 +5021,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="206" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="206" spans="1:4" ht="15" customHeight="1">
       <c r="A206" s="2" t="s">
         <v>297</v>
       </c>
@@ -5036,7 +5035,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="207" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="207" spans="1:4" ht="15" customHeight="1">
       <c r="A207" s="2" t="s">
         <v>298</v>
       </c>
@@ -5050,7 +5049,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="208" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="208" spans="1:4" ht="15" customHeight="1">
       <c r="A208" s="2" t="s">
         <v>299</v>
       </c>
@@ -5064,7 +5063,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="209" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="209" spans="1:4" ht="15" customHeight="1">
       <c r="A209" s="2" t="s">
         <v>301</v>
       </c>
@@ -5078,7 +5077,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="210" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="210" spans="1:4" ht="15" customHeight="1">
       <c r="A210" s="2" t="s">
         <v>302</v>
       </c>
@@ -5092,7 +5091,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="211" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="211" spans="1:4" ht="15" customHeight="1">
       <c r="A211" s="2" t="s">
         <v>304</v>
       </c>
@@ -5106,7 +5105,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="212" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="212" spans="1:4" ht="15" customHeight="1">
       <c r="A212" s="2" t="s">
         <v>305</v>
       </c>
@@ -5120,7 +5119,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="213" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="213" spans="1:4" ht="15" customHeight="1">
       <c r="A213" s="2" t="s">
         <v>306</v>
       </c>
@@ -5134,7 +5133,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="214" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="214" spans="1:4" ht="15" customHeight="1">
       <c r="A214" s="2" t="s">
         <v>307</v>
       </c>
@@ -5148,7 +5147,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="215" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="215" spans="1:4" ht="15" customHeight="1">
       <c r="A215" s="2" t="s">
         <v>308</v>
       </c>
@@ -5162,7 +5161,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="216" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="216" spans="1:4" ht="15" customHeight="1">
       <c r="A216" s="2" t="s">
         <v>309</v>
       </c>
@@ -5176,7 +5175,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="217" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="217" spans="1:4" ht="15" customHeight="1">
       <c r="A217" s="2" t="s">
         <v>310</v>
       </c>
@@ -5190,7 +5189,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="218" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="218" spans="1:4" ht="15" customHeight="1">
       <c r="A218" s="2" t="s">
         <v>311</v>
       </c>
@@ -5204,7 +5203,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="219" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="219" spans="1:4" ht="15" customHeight="1">
       <c r="A219" s="2" t="s">
         <v>313</v>
       </c>
@@ -5218,7 +5217,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="220" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="220" spans="1:4" ht="15" customHeight="1">
       <c r="A220" s="2" t="s">
         <v>314</v>
       </c>
@@ -5232,7 +5231,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="221" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="221" spans="1:4" ht="15" customHeight="1">
       <c r="A221" s="2" t="s">
         <v>315</v>
       </c>
@@ -5246,7 +5245,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="222" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="222" spans="1:4" ht="15" customHeight="1">
       <c r="A222" s="2" t="s">
         <v>317</v>
       </c>
@@ -5260,7 +5259,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="223" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="223" spans="1:4" ht="15" customHeight="1">
       <c r="A223" s="2" t="s">
         <v>319</v>
       </c>
@@ -5274,7 +5273,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="224" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="224" spans="1:4" ht="15" customHeight="1">
       <c r="A224" s="2" t="s">
         <v>320</v>
       </c>
@@ -5288,7 +5287,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="225" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="225" spans="1:4" ht="15" customHeight="1">
       <c r="A225" s="2" t="s">
         <v>322</v>
       </c>
@@ -5302,7 +5301,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="226" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="226" spans="1:4" ht="15" customHeight="1">
       <c r="A226" s="2" t="s">
         <v>323</v>
       </c>
@@ -5316,7 +5315,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="227" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="227" spans="1:4" ht="15" customHeight="1">
       <c r="A227" s="2" t="s">
         <v>325</v>
       </c>
@@ -5330,7 +5329,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="228" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="228" spans="1:4" ht="15" customHeight="1">
       <c r="A228" s="2" t="s">
         <v>327</v>
       </c>
@@ -5344,7 +5343,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="229" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="229" spans="1:4" ht="15" customHeight="1">
       <c r="A229" s="2" t="s">
         <v>329</v>
       </c>
@@ -5358,7 +5357,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="230" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="230" spans="1:4" ht="15" customHeight="1">
       <c r="A230" s="2" t="s">
         <v>330</v>
       </c>
@@ -5372,7 +5371,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="231" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="231" spans="1:4" ht="15" customHeight="1">
       <c r="A231" s="2" t="s">
         <v>331</v>
       </c>
@@ -5386,7 +5385,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="232" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="232" spans="1:4" ht="15" customHeight="1">
       <c r="A232" s="2" t="s">
         <v>332</v>
       </c>
@@ -5400,7 +5399,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="233" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="233" spans="1:4" ht="15" customHeight="1">
       <c r="A233" s="2" t="s">
         <v>334</v>
       </c>
@@ -5414,7 +5413,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="234" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="234" spans="1:4" ht="15" customHeight="1">
       <c r="A234" s="2" t="s">
         <v>336</v>
       </c>
@@ -5428,7 +5427,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="235" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="235" spans="1:4" ht="15" customHeight="1">
       <c r="A235" s="2" t="s">
         <v>338</v>
       </c>
@@ -5442,7 +5441,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="236" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="236" spans="1:4" ht="15" customHeight="1">
       <c r="A236" s="2" t="s">
         <v>340</v>
       </c>
@@ -5456,7 +5455,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="237" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="237" spans="1:4" ht="15" customHeight="1">
       <c r="A237" s="2" t="s">
         <v>341</v>
       </c>
@@ -5470,7 +5469,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="238" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="238" spans="1:4" ht="15" customHeight="1">
       <c r="A238" s="2" t="s">
         <v>342</v>
       </c>
@@ -5484,7 +5483,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="239" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="239" spans="1:4" ht="15" customHeight="1">
       <c r="A239" s="2" t="s">
         <v>343</v>
       </c>
@@ -5498,7 +5497,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="240" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="240" spans="1:4" ht="15" customHeight="1">
       <c r="A240" s="2" t="s">
         <v>344</v>
       </c>
@@ -5512,7 +5511,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="241" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="241" spans="1:4" ht="15" customHeight="1">
       <c r="A241" s="2" t="s">
         <v>345</v>
       </c>
@@ -5526,7 +5525,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="242" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="242" spans="1:4" ht="15" customHeight="1">
       <c r="A242" s="2" t="s">
         <v>347</v>
       </c>
@@ -5540,7 +5539,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="243" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="243" spans="1:4" ht="15" customHeight="1">
       <c r="A243" s="2" t="s">
         <v>349</v>
       </c>
@@ -5554,7 +5553,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="244" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="244" spans="1:4" ht="15" customHeight="1">
       <c r="A244" s="2" t="s">
         <v>351</v>
       </c>
@@ -5568,7 +5567,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="245" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="245" spans="1:4" ht="15" customHeight="1">
       <c r="A245" s="2" t="s">
         <v>352</v>
       </c>
@@ -5582,7 +5581,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="246" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="246" spans="1:4" ht="15" customHeight="1">
       <c r="A246" s="2" t="s">
         <v>353</v>
       </c>
@@ -5596,7 +5595,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="247" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="247" spans="1:4" ht="15" customHeight="1">
       <c r="A247" s="2" t="s">
         <v>355</v>
       </c>
@@ -5610,7 +5609,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="248" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="248" spans="1:4" ht="15" customHeight="1">
       <c r="A248" s="2" t="s">
         <v>356</v>
       </c>
@@ -5624,7 +5623,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="249" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="249" spans="1:4" ht="15" customHeight="1">
       <c r="A249" s="2" t="s">
         <v>357</v>
       </c>
@@ -5638,7 +5637,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="250" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="250" spans="1:4" ht="15" customHeight="1">
       <c r="A250" s="2" t="s">
         <v>358</v>
       </c>
@@ -5652,7 +5651,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="251" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="251" spans="1:4" ht="15" customHeight="1">
       <c r="A251" s="2" t="s">
         <v>359</v>
       </c>
@@ -5666,7 +5665,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="252" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="252" spans="1:4" ht="15" customHeight="1">
       <c r="A252" s="2" t="s">
         <v>360</v>
       </c>
@@ -5680,7 +5679,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="253" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="253" spans="1:4" ht="15" customHeight="1">
       <c r="A253" s="2" t="s">
         <v>361</v>
       </c>
@@ -5694,7 +5693,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="254" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="254" spans="1:4" ht="15" customHeight="1">
       <c r="A254" s="2" t="s">
         <v>362</v>
       </c>
@@ -5708,7 +5707,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="255" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="255" spans="1:4" ht="15" customHeight="1">
       <c r="A255" s="2" t="s">
         <v>364</v>
       </c>
@@ -5722,7 +5721,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="256" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="256" spans="1:4" ht="15" customHeight="1">
       <c r="A256" s="2" t="s">
         <v>366</v>
       </c>
@@ -5736,7 +5735,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="257" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="257" spans="1:4" ht="15" customHeight="1">
       <c r="A257" s="2" t="s">
         <v>367</v>
       </c>
@@ -5750,7 +5749,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="258" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="258" spans="1:4" ht="15" customHeight="1">
       <c r="A258" s="2" t="s">
         <v>368</v>
       </c>
@@ -5764,7 +5763,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="259" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="259" spans="1:4" ht="15" customHeight="1">
       <c r="A259" s="2" t="s">
         <v>369</v>
       </c>
@@ -5778,7 +5777,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="260" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="260" spans="1:4" ht="15" customHeight="1">
       <c r="A260" s="2" t="s">
         <v>370</v>
       </c>
@@ -5792,7 +5791,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="261" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="261" spans="1:4" ht="15" customHeight="1">
       <c r="A261" s="2" t="s">
         <v>371</v>
       </c>
@@ -5806,7 +5805,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="262" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="262" spans="1:4" ht="15" customHeight="1">
       <c r="A262" s="2" t="s">
         <v>373</v>
       </c>
@@ -5820,7 +5819,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="263" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="263" spans="1:4" ht="15" customHeight="1">
       <c r="A263" s="2" t="s">
         <v>374</v>
       </c>
@@ -5834,7 +5833,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="264" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="264" spans="1:4" ht="15" customHeight="1">
       <c r="A264" s="2" t="s">
         <v>375</v>
       </c>
@@ -5848,7 +5847,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="265" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="265" spans="1:4" ht="15" customHeight="1">
       <c r="A265" s="2" t="s">
         <v>376</v>
       </c>
@@ -5862,7 +5861,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="266" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="266" spans="1:4" ht="15" customHeight="1">
       <c r="A266" s="2" t="s">
         <v>378</v>
       </c>
@@ -5876,7 +5875,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="267" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="267" spans="1:4" ht="15" customHeight="1">
       <c r="A267" s="2" t="s">
         <v>379</v>
       </c>
@@ -5890,7 +5889,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="268" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="268" spans="1:4" ht="15" customHeight="1">
       <c r="A268" s="2" t="s">
         <v>380</v>
       </c>
@@ -5904,7 +5903,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="269" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="269" spans="1:4" ht="15" customHeight="1">
       <c r="A269" s="2" t="s">
         <v>382</v>
       </c>
@@ -5918,7 +5917,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="270" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="270" spans="1:4" ht="15" customHeight="1">
       <c r="A270" s="2" t="s">
         <v>383</v>
       </c>
@@ -5932,7 +5931,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="271" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="271" spans="1:4" ht="15" customHeight="1">
       <c r="A271" s="2" t="s">
         <v>384</v>
       </c>
@@ -5946,7 +5945,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="272" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="272" spans="1:4" ht="15" customHeight="1">
       <c r="A272" s="2" t="s">
         <v>385</v>
       </c>
@@ -5960,7 +5959,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="273" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="273" spans="1:4" ht="15" customHeight="1">
       <c r="A273" s="2" t="s">
         <v>386</v>
       </c>
@@ -5974,7 +5973,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="274" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="274" spans="1:4" ht="15" customHeight="1">
       <c r="A274" s="2" t="s">
         <v>387</v>
       </c>
@@ -5988,7 +5987,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="275" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="275" spans="1:4" ht="15" customHeight="1">
       <c r="A275" s="2" t="s">
         <v>389</v>
       </c>
@@ -6002,7 +6001,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="276" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="276" spans="1:4" ht="15" customHeight="1">
       <c r="A276" s="2" t="s">
         <v>390</v>
       </c>
@@ -6016,7 +6015,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="277" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="277" spans="1:4" ht="15" customHeight="1">
       <c r="A277" s="2" t="s">
         <v>391</v>
       </c>
@@ -6030,7 +6029,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="278" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="278" spans="1:4" ht="15" customHeight="1">
       <c r="A278" s="2" t="s">
         <v>392</v>
       </c>
@@ -6044,7 +6043,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="279" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="279" spans="1:4" ht="15" customHeight="1">
       <c r="A279" s="2" t="s">
         <v>393</v>
       </c>
@@ -6058,7 +6057,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="280" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="280" spans="1:4" ht="15" customHeight="1">
       <c r="A280" s="2" t="s">
         <v>394</v>
       </c>
@@ -6072,7 +6071,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="281" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="281" spans="1:4" ht="15" customHeight="1">
       <c r="A281" s="2" t="s">
         <v>395</v>
       </c>
@@ -6086,7 +6085,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="282" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="282" spans="1:4" ht="15" customHeight="1">
       <c r="A282" s="2" t="s">
         <v>396</v>
       </c>
@@ -6100,7 +6099,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="283" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="283" spans="1:4" ht="15" customHeight="1">
       <c r="A283" s="2" t="s">
         <v>397</v>
       </c>
@@ -6114,7 +6113,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="284" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="284" spans="1:4" ht="15" customHeight="1">
       <c r="A284" s="2" t="s">
         <v>398</v>
       </c>
@@ -6128,7 +6127,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="285" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="285" spans="1:4" ht="15" customHeight="1">
       <c r="A285" s="2" t="s">
         <v>399</v>
       </c>
@@ -6142,7 +6141,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="286" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="286" spans="1:4" ht="15" customHeight="1">
       <c r="A286" s="2" t="s">
         <v>400</v>
       </c>
@@ -6156,7 +6155,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="287" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="287" spans="1:4" ht="15" customHeight="1">
       <c r="A287" s="2" t="s">
         <v>401</v>
       </c>
@@ -6170,7 +6169,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="288" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="288" spans="1:4" ht="15" customHeight="1">
       <c r="A288" s="2" t="s">
         <v>402</v>
       </c>
@@ -6184,7 +6183,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="289" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="289" spans="1:4" ht="15" customHeight="1">
       <c r="A289" s="2" t="s">
         <v>403</v>
       </c>
@@ -6198,7 +6197,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="290" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="290" spans="1:4" ht="15" customHeight="1">
       <c r="A290" s="2" t="s">
         <v>404</v>
       </c>
@@ -6212,7 +6211,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="291" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="291" spans="1:4" ht="15" customHeight="1">
       <c r="A291" s="2" t="s">
         <v>405</v>
       </c>
@@ -6226,7 +6225,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="292" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="292" spans="1:4" ht="15" customHeight="1">
       <c r="A292" s="2" t="s">
         <v>407</v>
       </c>
@@ -6240,7 +6239,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="293" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="293" spans="1:4" ht="15" customHeight="1">
       <c r="A293" s="2" t="s">
         <v>408</v>
       </c>
@@ -6254,7 +6253,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="294" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="294" spans="1:4" ht="15" customHeight="1">
       <c r="A294" s="2" t="s">
         <v>410</v>
       </c>
@@ -6268,7 +6267,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="295" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="295" spans="1:4" ht="15" customHeight="1">
       <c r="A295" s="2" t="s">
         <v>411</v>
       </c>
@@ -6282,7 +6281,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="296" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="296" spans="1:4" ht="15" customHeight="1">
       <c r="A296" s="2" t="s">
         <v>412</v>
       </c>
@@ -6296,7 +6295,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="297" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="297" spans="1:4" ht="15" customHeight="1">
       <c r="A297" s="2" t="s">
         <v>414</v>
       </c>
@@ -6310,7 +6309,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="298" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="298" spans="1:4" ht="15" customHeight="1">
       <c r="A298" s="2" t="s">
         <v>415</v>
       </c>
@@ -6324,7 +6323,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="299" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="299" spans="1:4" ht="15" customHeight="1">
       <c r="A299" s="2" t="s">
         <v>416</v>
       </c>
@@ -6338,7 +6337,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="300" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="300" spans="1:4" ht="15" customHeight="1">
       <c r="A300" s="2" t="s">
         <v>418</v>
       </c>
@@ -6352,7 +6351,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="301" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="301" spans="1:4" ht="15" customHeight="1">
       <c r="A301" s="2" t="s">
         <v>419</v>
       </c>
@@ -6366,7 +6365,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="302" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="302" spans="1:4" ht="15" customHeight="1">
       <c r="A302" s="2" t="s">
         <v>421</v>
       </c>
@@ -6380,7 +6379,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="303" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="303" spans="1:4" ht="15" customHeight="1">
       <c r="A303" s="2" t="s">
         <v>423</v>
       </c>
@@ -6394,7 +6393,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="304" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="304" spans="1:4" ht="15" customHeight="1">
       <c r="A304" s="2" t="s">
         <v>425</v>
       </c>
@@ -6408,7 +6407,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="305" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="305" spans="1:4" ht="15" customHeight="1">
       <c r="A305" s="2" t="s">
         <v>427</v>
       </c>
@@ -6422,7 +6421,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="306" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="306" spans="1:4" ht="15" customHeight="1">
       <c r="A306" s="2" t="s">
         <v>429</v>
       </c>
@@ -6436,7 +6435,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="307" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="307" spans="1:4" ht="15" customHeight="1">
       <c r="A307" s="2" t="s">
         <v>431</v>
       </c>
@@ -6450,7 +6449,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="308" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="308" spans="1:4" ht="15" customHeight="1">
       <c r="A308" s="2" t="s">
         <v>433</v>
       </c>
@@ -6464,7 +6463,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="309" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="309" spans="1:4" ht="15" customHeight="1">
       <c r="A309" s="2" t="s">
         <v>435</v>
       </c>
@@ -6478,7 +6477,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="310" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="310" spans="1:4" ht="15" customHeight="1">
       <c r="A310" s="2" t="s">
         <v>437</v>
       </c>
@@ -6492,7 +6491,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="311" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="311" spans="1:4" ht="15" customHeight="1">
       <c r="A311" s="2" t="s">
         <v>439</v>
       </c>
@@ -6506,7 +6505,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="312" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="312" spans="1:4" ht="15" customHeight="1">
       <c r="A312" s="2" t="s">
         <v>441</v>
       </c>
@@ -6520,7 +6519,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="313" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="313" spans="1:4" ht="15" customHeight="1">
       <c r="A313" s="2" t="s">
         <v>442</v>
       </c>
@@ -6534,7 +6533,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="314" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="314" spans="1:4" ht="15" customHeight="1">
       <c r="A314" s="2" t="s">
         <v>444</v>
       </c>
@@ -6548,7 +6547,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="315" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="315" spans="1:4" ht="15" customHeight="1">
       <c r="A315" s="2" t="s">
         <v>446</v>
       </c>
@@ -6562,7 +6561,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="316" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="316" spans="1:4" ht="15" customHeight="1">
       <c r="A316" s="2" t="s">
         <v>448</v>
       </c>
@@ -6576,7 +6575,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="317" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="317" spans="1:4" ht="15" customHeight="1">
       <c r="A317" s="2" t="s">
         <v>448</v>
       </c>
@@ -7178,7 +7177,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="360" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="360" spans="1:4" ht="15" customHeight="1">
       <c r="A360" s="2" t="s">
         <v>523</v>
       </c>
@@ -7192,7 +7191,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="361" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="361" spans="1:4" ht="15" customHeight="1">
       <c r="A361" s="2" t="s">
         <v>526</v>
       </c>
@@ -7206,7 +7205,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="362" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="362" spans="1:4" ht="15" customHeight="1">
       <c r="A362" s="2" t="s">
         <v>528</v>
       </c>
@@ -7220,7 +7219,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="363" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="363" spans="1:4" ht="15" customHeight="1">
       <c r="A363" s="2" t="s">
         <v>530</v>
       </c>
@@ -7234,7 +7233,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="364" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="364" spans="1:4" ht="15" customHeight="1">
       <c r="A364" s="2" t="s">
         <v>532</v>
       </c>
@@ -7248,7 +7247,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="365" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="365" spans="1:4" ht="15" customHeight="1">
       <c r="A365" s="2" t="s">
         <v>534</v>
       </c>
@@ -7262,7 +7261,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="366" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="366" spans="1:4" ht="15" customHeight="1">
       <c r="A366" s="2" t="s">
         <v>536</v>
       </c>
@@ -7276,7 +7275,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="367" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="367" spans="1:4" ht="15" customHeight="1">
       <c r="A367" s="2" t="s">
         <v>538</v>
       </c>
@@ -7290,7 +7289,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="368" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="368" spans="1:4" ht="15" customHeight="1">
       <c r="A368" s="2" t="s">
         <v>540</v>
       </c>
@@ -7304,7 +7303,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="369" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="369" spans="1:4" ht="15" customHeight="1">
       <c r="A369" s="2" t="s">
         <v>542</v>
       </c>
@@ -7318,7 +7317,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="370" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="370" spans="1:4" ht="15" customHeight="1">
       <c r="A370" s="2" t="s">
         <v>545</v>
       </c>
@@ -7332,7 +7331,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="371" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="371" spans="1:4" ht="15" customHeight="1">
       <c r="A371" s="2" t="s">
         <v>547</v>
       </c>
@@ -7346,7 +7345,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="372" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="372" spans="1:4" ht="15" customHeight="1">
       <c r="A372" s="2" t="s">
         <v>549</v>
       </c>
@@ -7360,7 +7359,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="373" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="373" spans="1:4" ht="15" customHeight="1">
       <c r="A373" s="2" t="s">
         <v>552</v>
       </c>
@@ -7374,7 +7373,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="374" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="374" spans="1:4" ht="15" customHeight="1">
       <c r="A374" s="2" t="s">
         <v>554</v>
       </c>
@@ -7388,7 +7387,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="375" spans="1:4" ht="15" hidden="1" customHeight="1">
+    <row r="375" spans="1:4" ht="15" customHeight="1">
       <c r="A375" s="2" t="s">
         <v>556</v>
       </c>
@@ -7403,13 +7402,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D375" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="4 - Satisfied"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:D375" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -7417,7 +7410,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D3BBB97-36B2-4A6C-9269-968F87F0DA53}">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="13.28515625" customWidth="1"/>
@@ -7626,33 +7619,112 @@
         <v>34</v>
       </c>
     </row>
+    <row r="11" spans="1:6" ht="15">
+      <c r="A11" s="5">
+        <v>46113</v>
+      </c>
+      <c r="B11" s="7">
+        <v>1</v>
+      </c>
+      <c r="C11" s="7">
+        <v>0</v>
+      </c>
+      <c r="D11" s="7">
+        <v>2</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0</v>
+      </c>
+      <c r="F11" s="7">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15">
+      <c r="A12" s="5">
+        <v>46143</v>
+      </c>
+      <c r="B12" s="7">
+        <v>2</v>
+      </c>
+      <c r="C12" s="7">
+        <v>0</v>
+      </c>
+      <c r="D12" s="7">
+        <v>0</v>
+      </c>
+      <c r="E12" s="7">
+        <v>5</v>
+      </c>
+      <c r="F12" s="7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15">
+      <c r="A13" s="5">
+        <v>46174</v>
+      </c>
+      <c r="B13" s="7">
+        <v>0</v>
+      </c>
+      <c r="C13" s="7">
+        <v>0</v>
+      </c>
+      <c r="D13" s="7">
+        <v>1</v>
+      </c>
+      <c r="E13" s="7">
+        <v>5</v>
+      </c>
+      <c r="F13" s="7">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15">
+      <c r="A14" s="5">
+        <v>46204</v>
+      </c>
+      <c r="B14" s="7">
+        <v>2</v>
+      </c>
+      <c r="C14" s="7">
+        <v>0</v>
+      </c>
+      <c r="D14" s="7">
+        <v>0</v>
+      </c>
+      <c r="E14" s="7">
+        <v>2</v>
+      </c>
+      <c r="F14" s="7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15">
+      <c r="A15" s="5">
+        <v>46235</v>
+      </c>
+      <c r="B15" s="7">
+        <v>2</v>
+      </c>
+      <c r="C15" s="7">
+        <v>1</v>
+      </c>
+      <c r="D15" s="7">
+        <v>0</v>
+      </c>
+      <c r="E15" s="7">
+        <v>6</v>
+      </c>
+      <c r="F15" s="7">
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Whatfor_x003f_ xmlns="2ee2d9e9-b7c3-4f8e-9687-c946c1044a73" xsi:nil="true"/>
-    <TaxCatchAll xmlns="dc4dcb21-90d3-4695-adc8-464bc3ea11a9" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2ee2d9e9-b7c3-4f8e-9687-c946c1044a73">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010071D348EA6C2F134F8CCD7A14FAB5DA39" ma:contentTypeVersion="20" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a0a68d9dfe8c1d188178482050519e57">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2ee2d9e9-b7c3-4f8e-9687-c946c1044a73" xmlns:ns3="dc4dcb21-90d3-4695-adc8-464bc3ea11a9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d6a210401e4afca4fde04e1ac7d5fad7" ns2:_="" ns3:_="">
     <xsd:import namespace="2ee2d9e9-b7c3-4f8e-9687-c946c1044a73"/>
@@ -7921,8 +7993,29 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Whatfor_x003f_ xmlns="2ee2d9e9-b7c3-4f8e-9687-c946c1044a73" xsi:nil="true"/>
+    <TaxCatchAll xmlns="dc4dcb21-90d3-4695-adc8-464bc3ea11a9" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2ee2d9e9-b7c3-4f8e-9687-c946c1044a73">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D65E716-B97F-49A8-8EE7-289850D1C55D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{671E1ABD-9AC8-4F52-93B8-C0B88BEBB60D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7930,7 +8023,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{671E1ABD-9AC8-4F52-93B8-C0B88BEBB60D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D65E716-B97F-49A8-8EE7-289850D1C55D}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
